--- a/data/trans_orig/P62A$jubilacion-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P62A$jubilacion-Edad-trans_orig.xlsx
@@ -1194,7 +1194,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>3852</t>
+          <t>4046</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1209,7 +1209,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>73,7%</t>
+          <t>77,42%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4981</t>
+          <t>5257</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1279,7 +1279,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>31,12%</t>
+          <t>32,84%</t>
         </is>
       </c>
     </row>
@@ -1342,7 +1342,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>5699</t>
+          <t>5773</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1357,7 +1357,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>52,87%</t>
+          <t>53,56%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1377,7 +1377,7 @@
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>5739</t>
+          <t>5856</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1392,7 +1392,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>35,85%</t>
+          <t>36,59%</t>
         </is>
       </c>
     </row>
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>784</t>
+          <t>787</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>6358</t>
+          <t>6407</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>58,98%</t>
+          <t>59,43%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2493</t>
+          <t>2460</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>10468</t>
+          <t>10519</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>15,58%</t>
+          <t>15,37%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>65,4%</t>
+          <t>65,72%</t>
         </is>
       </c>
     </row>
@@ -1533,7 +1533,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3471</t>
+          <t>4084</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1548,7 +1548,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>66,42%</t>
+          <t>78,14%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1563,12 +1563,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2168</t>
+          <t>2297</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>8996</t>
+          <t>8964</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1578,12 +1578,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>20,12%</t>
+          <t>21,31%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>83,45%</t>
+          <t>83,16%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>2999</t>
+          <t>2974</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>10935</t>
+          <t>10836</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>18,74%</t>
+          <t>18,58%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>68,32%</t>
+          <t>67,7%</t>
         </is>
       </c>
     </row>
@@ -1645,12 +1645,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3762</t>
+          <t>3773</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>13345</t>
+          <t>14220</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1660,12 +1660,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>15,0%</t>
+          <t>15,05%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>53,23%</t>
+          <t>56,72%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1680,12 +1680,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>907</t>
+          <t>926</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>6989</t>
+          <t>6918</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1695,12 +1695,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>36,24%</t>
+          <t>35,87%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1715,12 +1715,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>5846</t>
+          <t>5886</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>17828</t>
+          <t>18812</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1730,12 +1730,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>13,18%</t>
+          <t>13,27%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>40,19%</t>
+          <t>42,41%</t>
         </is>
       </c>
     </row>
@@ -1793,12 +1793,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>898</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>7110</t>
+          <t>6177</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1808,12 +1808,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>36,86%</t>
+          <t>32,03%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1828,12 +1828,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>935</t>
+          <t>923</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>8090</t>
+          <t>7884</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,12 +1843,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>18,24%</t>
+          <t>17,78%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>9703</t>
+          <t>9451</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>19976</t>
+          <t>19708</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>38,7%</t>
+          <t>37,7%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>79,69%</t>
+          <t>78,61%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>6010</t>
+          <t>5819</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>14455</t>
+          <t>14228</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>31,16%</t>
+          <t>30,17%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>74,95%</t>
+          <t>73,77%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>18752</t>
+          <t>18101</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>32533</t>
+          <t>31895</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>42,28%</t>
+          <t>40,81%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>73,35%</t>
+          <t>71,91%</t>
         </is>
       </c>
     </row>
@@ -1989,7 +1989,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>5974</t>
+          <t>5954</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2004,7 +2004,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>23,83%</t>
+          <t>23,75%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2019,12 +2019,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>941</t>
+          <t>926</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>7266</t>
+          <t>7009</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2034,12 +2034,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>37,67%</t>
+          <t>36,34%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2054,12 +2054,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1843</t>
+          <t>1858</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>10885</t>
+          <t>10222</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2069,12 +2069,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>24,54%</t>
+          <t>23,05%</t>
         </is>
       </c>
     </row>
@@ -2101,12 +2101,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>11643</t>
+          <t>12267</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>24912</t>
+          <t>25344</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2116,12 +2116,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>25,42%</t>
+          <t>26,79%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>54,4%</t>
+          <t>55,34%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2136,12 +2136,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>6748</t>
+          <t>6758</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>17914</t>
+          <t>18452</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2151,12 +2151,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>16,43%</t>
+          <t>16,46%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>43,63%</t>
+          <t>44,94%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>21127</t>
+          <t>22115</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>38668</t>
+          <t>39466</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2186,12 +2186,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>24,32%</t>
+          <t>25,46%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>44,52%</t>
+          <t>45,44%</t>
         </is>
       </c>
     </row>
@@ -2219,7 +2219,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>5349</t>
+          <t>5381</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2234,7 +2234,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>11,68%</t>
+          <t>11,75%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2249,12 +2249,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>6207</t>
+          <t>6001</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>17540</t>
+          <t>17228</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2264,12 +2264,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>15,12%</t>
+          <t>14,62%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>42,72%</t>
+          <t>41,96%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6288</t>
+          <t>6866</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>19982</t>
+          <t>19718</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>7,91%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>23,01%</t>
+          <t>22,7%</t>
         </is>
       </c>
     </row>
@@ -2327,12 +2327,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>18629</t>
+          <t>18051</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>32535</t>
+          <t>31729</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2342,12 +2342,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>40,68%</t>
+          <t>39,42%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>71,05%</t>
+          <t>69,29%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2362,12 +2362,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>7141</t>
+          <t>7204</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>19373</t>
+          <t>18638</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2377,12 +2377,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>17,39%</t>
+          <t>17,54%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>47,18%</t>
+          <t>45,39%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2397,12 +2397,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>29243</t>
+          <t>28451</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>46529</t>
+          <t>47076</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2412,12 +2412,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>33,67%</t>
+          <t>32,76%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>53,57%</t>
+          <t>54,2%</t>
         </is>
       </c>
     </row>
@@ -2445,7 +2445,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>6357</t>
+          <t>4368</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2460,7 +2460,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>13,88%</t>
+          <t>9,54%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2475,12 +2475,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2885</t>
+          <t>1998</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>10859</t>
+          <t>10992</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2490,12 +2490,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>26,45%</t>
+          <t>26,77%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,12 +2510,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>2947</t>
+          <t>2957</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>12904</t>
+          <t>12985</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2525,12 +2525,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>14,86%</t>
+          <t>14,95%</t>
         </is>
       </c>
     </row>
@@ -2557,12 +2557,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>129902</t>
+          <t>131142</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>148916</t>
+          <t>149204</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2572,12 +2572,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>76,95%</t>
+          <t>77,69%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>88,22%</t>
+          <t>88,39%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2592,12 +2592,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>18794</t>
+          <t>19548</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>35972</t>
+          <t>35250</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2607,12 +2607,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>23,51%</t>
+          <t>24,46%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>45,01%</t>
+          <t>44,1%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>152343</t>
+          <t>153438</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>181262</t>
+          <t>181573</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2642,12 +2642,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>61,25%</t>
+          <t>61,69%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>72,87%</t>
+          <t>73,0%</t>
         </is>
       </c>
     </row>
@@ -2705,12 +2705,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>27579</t>
+          <t>27697</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>45558</t>
+          <t>45212</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2720,12 +2720,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>34,51%</t>
+          <t>34,65%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>57,0%</t>
+          <t>56,57%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2740,12 +2740,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>25960</t>
+          <t>25902</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>47046</t>
+          <t>46576</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2755,12 +2755,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>10,44%</t>
+          <t>10,41%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>18,91%</t>
+          <t>18,73%</t>
         </is>
       </c>
     </row>
@@ -2783,12 +2783,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>19065</t>
+          <t>18798</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>38107</t>
+          <t>37257</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2798,12 +2798,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>11,29%</t>
+          <t>11,14%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>22,57%</t>
+          <t>22,07%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,12 +2818,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>8019</t>
+          <t>7500</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>22467</t>
+          <t>21765</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2833,12 +2833,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>10,03%</t>
+          <t>9,38%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>28,11%</t>
+          <t>27,23%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,12 +2853,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>29785</t>
+          <t>30879</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>54066</t>
+          <t>52577</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2868,12 +2868,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>11,97%</t>
+          <t>12,41%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>21,74%</t>
+          <t>21,14%</t>
         </is>
       </c>
     </row>
@@ -2901,7 +2901,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>4244</t>
+          <t>3979</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2916,7 +2916,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2931,12 +2931,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>974</t>
+          <t>978</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>9127</t>
+          <t>8420</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2951,7 +2951,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>11,42%</t>
+          <t>10,54%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2966,12 +2966,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>991</t>
+          <t>1206</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>10341</t>
+          <t>9784</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2981,12 +2981,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>3,93%</t>
         </is>
       </c>
     </row>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>277542</t>
+          <t>278067</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>284796</t>
+          <t>285674</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3028,12 +3028,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>97,15%</t>
+          <t>97,34%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>99,69%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3048,12 +3048,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>73757</t>
+          <t>73601</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>99021</t>
+          <t>98966</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>41,73%</t>
+          <t>41,64%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>56,03%</t>
+          <t>56,0%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3083,12 +3083,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>352669</t>
+          <t>352256</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>385274</t>
+          <t>387105</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3098,12 +3098,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>76,27%</t>
+          <t>76,18%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>83,32%</t>
+          <t>83,71%</t>
         </is>
       </c>
     </row>
@@ -3131,7 +3131,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>5552</t>
+          <t>5834</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3161,12 +3161,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>71405</t>
+          <t>70744</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>96096</t>
+          <t>96474</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3176,12 +3176,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>40,4%</t>
+          <t>40,03%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>54,37%</t>
+          <t>54,59%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3196,12 +3196,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>69181</t>
+          <t>67624</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>101620</t>
+          <t>102405</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3211,12 +3211,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>14,96%</t>
+          <t>14,62%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>21,98%</t>
+          <t>22,15%</t>
         </is>
       </c>
     </row>
@@ -3244,7 +3244,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>4723</t>
+          <t>4700</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3274,12 +3274,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1832</t>
+          <t>1844</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>11180</t>
+          <t>11892</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3294,7 +3294,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>6,73%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3309,12 +3309,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>2707</t>
+          <t>2198</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>12099</t>
+          <t>12275</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,65%</t>
         </is>
       </c>
     </row>
@@ -3357,7 +3357,7 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>4816</t>
+          <t>5045</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3372,7 +3372,7 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3387,12 +3387,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>888</t>
+          <t>882</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>7875</t>
+          <t>7814</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3407,7 +3407,7 @@
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3422,12 +3422,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1658</t>
+          <t>1683</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>9665</t>
+          <t>9590</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3442,7 +3442,7 @@
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,07%</t>
         </is>
       </c>
     </row>
@@ -3504,12 +3504,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>80833</t>
+          <t>81160</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>113591</t>
+          <t>112294</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3519,12 +3519,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>32,69%</t>
+          <t>32,82%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>45,93%</t>
+          <t>45,41%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3539,12 +3539,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>279719</t>
+          <t>282199</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>323479</t>
+          <t>324901</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3554,12 +3554,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>61,66%</t>
+          <t>62,2%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>71,3%</t>
+          <t>71,61%</t>
         </is>
       </c>
     </row>
@@ -3617,12 +3617,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>131549</t>
+          <t>132281</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>163770</t>
+          <t>162840</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3632,12 +3632,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>53,19%</t>
+          <t>53,49%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>66,22%</t>
+          <t>65,85%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3652,12 +3652,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>129216</t>
+          <t>128128</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>171514</t>
+          <t>169366</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3667,12 +3667,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>28,48%</t>
+          <t>28,24%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>37,8%</t>
+          <t>37,33%</t>
         </is>
       </c>
     </row>
@@ -3730,12 +3730,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1053</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>8786</t>
+          <t>8877</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3745,47 +3745,47 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
+          <t>0,43%</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="inlineStr">
+        <is>
+          <t>3,59%</t>
+        </is>
+      </c>
+      <c r="Q30" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="R30" s="2" t="inlineStr">
+        <is>
+          <t>3329</t>
+        </is>
+      </c>
+      <c r="S30" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T30" s="2" t="inlineStr">
+        <is>
+          <t>8859</t>
+        </is>
+      </c>
+      <c r="U30" s="2" t="inlineStr">
+        <is>
+          <t>0,73%</t>
+        </is>
+      </c>
+      <c r="V30" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P30" s="2" t="inlineStr">
-        <is>
-          <t>3,55%</t>
-        </is>
-      </c>
-      <c r="Q30" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="R30" s="2" t="inlineStr">
-        <is>
-          <t>3329</t>
-        </is>
-      </c>
-      <c r="S30" s="2" t="inlineStr">
-        <is>
-          <t>1062</t>
-        </is>
-      </c>
-      <c r="T30" s="2" t="inlineStr">
-        <is>
-          <t>9082</t>
-        </is>
-      </c>
-      <c r="U30" s="2" t="inlineStr">
-        <is>
-          <t>0,73%</t>
-        </is>
-      </c>
-      <c r="V30" s="2" t="inlineStr">
-        <is>
-          <t>0,23%</t>
-        </is>
-      </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,95%</t>
         </is>
       </c>
     </row>
@@ -3843,12 +3843,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>1135</t>
+          <t>1318</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>11570</t>
+          <t>11407</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3858,12 +3858,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3883,7 +3883,7 @@
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>11742</t>
+          <t>12642</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3898,7 +3898,7 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,79%</t>
         </is>
       </c>
     </row>
@@ -3925,12 +3925,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>638499</t>
+          <t>639437</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>672924</t>
+          <t>672786</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3940,12 +3940,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>86,53%</t>
+          <t>86,66%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>91,2%</t>
+          <t>91,18%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3960,12 +3960,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>201156</t>
+          <t>202254</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>247086</t>
+          <t>249874</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3975,12 +3975,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>34,92%</t>
+          <t>35,11%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>42,89%</t>
+          <t>43,37%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3995,12 +3995,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>847160</t>
+          <t>850179</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>914828</t>
+          <t>919693</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -4010,12 +4010,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>64,47%</t>
+          <t>64,7%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>69,62%</t>
+          <t>69,99%</t>
         </is>
       </c>
     </row>
@@ -4043,7 +4043,7 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>6964</t>
+          <t>6903</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4073,12 +4073,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>262575</t>
+          <t>261261</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>309304</t>
+          <t>309755</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4088,12 +4088,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>45,58%</t>
+          <t>45,35%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>53,69%</t>
+          <t>53,77%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4108,12 +4108,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>256818</t>
+          <t>255092</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>314441</t>
+          <t>312903</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4123,12 +4123,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>19,55%</t>
+          <t>19,41%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>23,93%</t>
+          <t>23,81%</t>
         </is>
       </c>
     </row>
@@ -4151,12 +4151,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>57073</t>
+          <t>58227</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>90981</t>
+          <t>90227</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4166,12 +4166,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>7,89%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>12,33%</t>
+          <t>12,23%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4186,12 +4186,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>35221</t>
+          <t>35608</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>63012</t>
+          <t>60881</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4201,12 +4201,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>6,18%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>10,94%</t>
+          <t>10,57%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4221,12 +4221,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>100677</t>
+          <t>99271</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>140889</t>
+          <t>142305</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4236,12 +4236,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>7,56%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>10,72%</t>
+          <t>10,83%</t>
         </is>
       </c>
     </row>
@@ -4264,12 +4264,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>2795</t>
+          <t>2753</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>13718</t>
+          <t>12746</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4279,12 +4279,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4299,12 +4299,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>17283</t>
+          <t>18706</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>39179</t>
+          <t>40171</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4314,12 +4314,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>6,97%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4334,12 +4334,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>23990</t>
+          <t>23649</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>48784</t>
+          <t>46759</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4349,12 +4349,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,56%</t>
         </is>
       </c>
     </row>
@@ -4917,7 +4917,7 @@
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>5036</t>
+          <t>4325</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4932,7 +4932,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>37,01%</t>
+          <t>31,78%</t>
         </is>
       </c>
     </row>
@@ -5025,7 +5025,7 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>8572</t>
+          <t>9283</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
@@ -5040,7 +5040,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>62,99%</t>
+          <t>68,22%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -5190,7 +5190,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4077</t>
+          <t>4229</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -5205,7 +5205,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>24,34%</t>
+          <t>25,25%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -5260,7 +5260,7 @@
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>5090</t>
+          <t>4864</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5275,7 +5275,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>12,39%</t>
+          <t>11,84%</t>
         </is>
       </c>
     </row>
@@ -5298,12 +5298,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>5346</t>
+          <t>5716</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>13623</t>
+          <t>13714</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5313,12 +5313,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>31,92%</t>
+          <t>34,13%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>81,33%</t>
+          <t>81,87%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5333,12 +5333,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1065</t>
+          <t>1088</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>10630</t>
+          <t>10607</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>43,68%</t>
+          <t>43,59%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5368,12 +5368,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>8884</t>
+          <t>9062</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>21065</t>
+          <t>20917</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>21,62%</t>
+          <t>22,06%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>51,27%</t>
+          <t>50,91%</t>
         </is>
       </c>
     </row>
@@ -5411,12 +5411,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2185</t>
+          <t>2117</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>10712</t>
+          <t>10377</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5426,12 +5426,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>13,05%</t>
+          <t>12,64%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>63,95%</t>
+          <t>61,95%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5446,12 +5446,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>13705</t>
+          <t>13728</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>23270</t>
+          <t>23247</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>56,32%</t>
+          <t>56,41%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,62%</t>
+          <t>95,53%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5481,12 +5481,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>19028</t>
+          <t>19067</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>31588</t>
+          <t>31227</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>46,31%</t>
+          <t>46,41%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>76,89%</t>
+          <t>76,01%</t>
         </is>
       </c>
     </row>
@@ -5533,7 +5533,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>4171</t>
+          <t>3958</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5548,7 +5548,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>8,93%</t>
+          <t>8,47%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5603,7 +5603,7 @@
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>5159</t>
+          <t>5250</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5618,7 +5618,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>6,08%</t>
         </is>
       </c>
     </row>
@@ -5676,12 +5676,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>886</t>
+          <t>873</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>7861</t>
+          <t>7574</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>19,82%</t>
+          <t>19,09%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5711,12 +5711,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>898</t>
+          <t>871</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>7885</t>
+          <t>8140</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,13%</t>
+          <t>9,42%</t>
         </is>
       </c>
     </row>
@@ -5754,12 +5754,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>17944</t>
+          <t>18624</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>32974</t>
+          <t>32926</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5769,12 +5769,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>38,41%</t>
+          <t>39,86%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>70,57%</t>
+          <t>70,47%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5789,12 +5789,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>12625</t>
+          <t>12323</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>25634</t>
+          <t>25665</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>31,83%</t>
+          <t>31,07%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>64,62%</t>
+          <t>64,7%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5824,12 +5824,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>34117</t>
+          <t>33779</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>54776</t>
+          <t>54044</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>39,49%</t>
+          <t>39,1%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>63,41%</t>
+          <t>62,56%</t>
         </is>
       </c>
     </row>
@@ -5867,12 +5867,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>13334</t>
+          <t>13130</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>28487</t>
+          <t>27736</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -5882,12 +5882,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>28,54%</t>
+          <t>28,1%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>60,97%</t>
+          <t>59,36%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -5902,12 +5902,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>11201</t>
+          <t>11309</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>24340</t>
+          <t>24503</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5917,12 +5917,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>28,24%</t>
+          <t>28,51%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>61,36%</t>
+          <t>61,77%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -5937,12 +5937,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>28327</t>
+          <t>28360</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>48825</t>
+          <t>48610</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -5952,12 +5952,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>32,79%</t>
+          <t>32,83%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>56,52%</t>
+          <t>56,27%</t>
         </is>
       </c>
     </row>
@@ -5984,12 +5984,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2218</t>
+          <t>3061</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>12592</t>
+          <t>13374</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5999,12 +5999,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>16,61%</t>
+          <t>17,64%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6019,12 +6019,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>992</t>
+          <t>974</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>7988</t>
+          <t>8630</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>14,62%</t>
+          <t>15,8%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6054,12 +6054,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>4765</t>
+          <t>5059</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>16668</t>
+          <t>18038</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>12,78%</t>
+          <t>13,83%</t>
         </is>
       </c>
     </row>
@@ -6132,12 +6132,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>9168</t>
+          <t>8849</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>23629</t>
+          <t>23201</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>16,78%</t>
+          <t>16,2%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>43,25%</t>
+          <t>42,47%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6167,12 +6167,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>8157</t>
+          <t>9014</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>24041</t>
+          <t>25513</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>6,91%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>18,43%</t>
+          <t>19,56%</t>
         </is>
       </c>
     </row>
@@ -6210,12 +6210,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>45817</t>
+          <t>45423</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>62669</t>
+          <t>62015</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -6225,12 +6225,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>60,42%</t>
+          <t>59,9%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>82,65%</t>
+          <t>81,79%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6245,12 +6245,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>12297</t>
+          <t>12547</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>27776</t>
+          <t>26635</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6260,12 +6260,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>22,51%</t>
+          <t>22,96%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>50,84%</t>
+          <t>48,75%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6280,12 +6280,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>61860</t>
+          <t>61587</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>86457</t>
+          <t>86505</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6295,12 +6295,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>47,42%</t>
+          <t>47,21%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>66,27%</t>
+          <t>66,31%</t>
         </is>
       </c>
     </row>
@@ -6323,12 +6323,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>8075</t>
+          <t>7703</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>22256</t>
+          <t>22705</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -6338,12 +6338,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>10,65%</t>
+          <t>10,16%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>29,35%</t>
+          <t>29,94%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -6358,12 +6358,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>10118</t>
+          <t>10499</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>24046</t>
+          <t>24601</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6373,12 +6373,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>18,52%</t>
+          <t>19,22%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>44,01%</t>
+          <t>45,03%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -6393,12 +6393,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>22418</t>
+          <t>21607</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>42815</t>
+          <t>42789</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -6408,12 +6408,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>17,18%</t>
+          <t>16,56%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>32,82%</t>
+          <t>32,8%</t>
         </is>
       </c>
     </row>
@@ -6440,12 +6440,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>98327</t>
+          <t>98592</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>124739</t>
+          <t>125659</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6455,12 +6455,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>56,7%</t>
+          <t>56,85%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>71,93%</t>
+          <t>72,46%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6475,12 +6475,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>15928</t>
+          <t>16489</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>33981</t>
+          <t>32646</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6490,12 +6490,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>16,63%</t>
+          <t>17,22%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>35,49%</t>
+          <t>34,09%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6510,12 +6510,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>117506</t>
+          <t>118798</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>152807</t>
+          <t>152770</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6525,12 +6525,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>43,65%</t>
+          <t>44,13%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>56,77%</t>
+          <t>56,75%</t>
         </is>
       </c>
     </row>
@@ -6588,12 +6588,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>29244</t>
+          <t>30200</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>49084</t>
+          <t>49511</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -6603,12 +6603,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>30,54%</t>
+          <t>31,54%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>51,26%</t>
+          <t>51,71%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -6623,12 +6623,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>28280</t>
+          <t>29000</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>51628</t>
+          <t>52790</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -6638,12 +6638,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>10,51%</t>
+          <t>10,77%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>19,18%</t>
+          <t>19,61%</t>
         </is>
       </c>
     </row>
@@ -6666,12 +6666,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>34946</t>
+          <t>34549</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>59470</t>
+          <t>59636</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6681,12 +6681,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>20,15%</t>
+          <t>19,92%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>34,29%</t>
+          <t>34,39%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6701,12 +6701,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>17140</t>
+          <t>16779</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>35347</t>
+          <t>34528</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6716,12 +6716,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>17,9%</t>
+          <t>17,52%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>36,91%</t>
+          <t>36,06%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6736,12 +6736,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>57083</t>
+          <t>56480</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>88170</t>
+          <t>87119</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6751,12 +6751,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>21,21%</t>
+          <t>20,98%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>32,76%</t>
+          <t>32,36%</t>
         </is>
       </c>
     </row>
@@ -6779,12 +6779,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>8347</t>
+          <t>8172</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>24497</t>
+          <t>25320</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6794,12 +6794,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>14,13%</t>
+          <t>14,6%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6814,12 +6814,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3132</t>
+          <t>3225</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>15977</t>
+          <t>14728</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6829,12 +6829,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>16,69%</t>
+          <t>15,38%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6849,12 +6849,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>14262</t>
+          <t>14628</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>34539</t>
+          <t>33994</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6864,12 +6864,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>12,83%</t>
+          <t>12,63%</t>
         </is>
       </c>
     </row>
@@ -6896,12 +6896,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>289216</t>
+          <t>289524</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>303404</t>
+          <t>303486</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6911,12 +6911,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>94,62%</t>
+          <t>94,72%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>99,26%</t>
+          <t>99,29%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6931,12 +6931,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>114273</t>
+          <t>113721</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>143513</t>
+          <t>143119</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6946,12 +6946,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>50,66%</t>
+          <t>50,41%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>63,62%</t>
+          <t>63,44%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6966,12 +6966,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>408724</t>
+          <t>407105</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>445090</t>
+          <t>444515</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6981,12 +6981,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>76,94%</t>
+          <t>76,63%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>83,78%</t>
+          <t>83,67%</t>
         </is>
       </c>
     </row>
@@ -7014,7 +7014,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>8587</t>
+          <t>10514</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -7029,7 +7029,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -7044,12 +7044,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>74394</t>
+          <t>76403</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>103895</t>
+          <t>104343</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>32,98%</t>
+          <t>33,87%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>46,06%</t>
+          <t>46,26%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -7079,12 +7079,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>74539</t>
+          <t>75890</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>110631</t>
+          <t>109634</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -7094,12 +7094,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>14,03%</t>
+          <t>14,29%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>20,82%</t>
+          <t>20,64%</t>
         </is>
       </c>
     </row>
@@ -7122,12 +7122,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1098</t>
+          <t>1093</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>12076</t>
+          <t>11422</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -7142,7 +7142,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -7157,12 +7157,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>989</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>8902</t>
+          <t>8292</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -7177,7 +7177,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -7192,12 +7192,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>3094</t>
+          <t>3095</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>15643</t>
+          <t>16276</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -7212,7 +7212,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>3,06%</t>
         </is>
       </c>
     </row>
@@ -7240,7 +7240,7 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>5267</t>
+          <t>5697</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -7255,7 +7255,7 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -7270,12 +7270,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>7028</t>
+          <t>6898</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>20732</t>
+          <t>20119</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -7285,12 +7285,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>9,19%</t>
+          <t>8,92%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -7305,12 +7305,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>7951</t>
+          <t>8083</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>22602</t>
+          <t>22701</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -7320,12 +7320,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,27%</t>
         </is>
       </c>
     </row>
@@ -7352,7 +7352,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>244122</t>
+          <t>243521</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -7367,7 +7367,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>98,12%</t>
+          <t>97,88%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -7387,12 +7387,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>94034</t>
+          <t>92533</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>127001</t>
+          <t>126109</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7402,12 +7402,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>31,72%</t>
+          <t>31,21%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>42,84%</t>
+          <t>42,54%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7422,12 +7422,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>333912</t>
+          <t>332695</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>379041</t>
+          <t>380370</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7437,12 +7437,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>61,24%</t>
+          <t>61,02%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>69,52%</t>
+          <t>69,76%</t>
         </is>
       </c>
     </row>
@@ -7500,12 +7500,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>158477</t>
+          <t>159549</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>192792</t>
+          <t>193382</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7515,12 +7515,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>53,46%</t>
+          <t>53,82%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>65,04%</t>
+          <t>65,24%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7535,12 +7535,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>153910</t>
+          <t>152181</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>199339</t>
+          <t>199970</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7550,12 +7550,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>28,23%</t>
+          <t>27,91%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>36,56%</t>
+          <t>36,68%</t>
         </is>
       </c>
     </row>
@@ -7583,7 +7583,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>4667</t>
+          <t>5268</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7598,7 +7598,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7613,12 +7613,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>3246</t>
+          <t>3251</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>15152</t>
+          <t>15022</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7633,7 +7633,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7648,12 +7648,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>3326</t>
+          <t>4243</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>16251</t>
+          <t>15978</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7663,12 +7663,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>2,93%</t>
         </is>
       </c>
     </row>
@@ -7726,12 +7726,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>5465</t>
+          <t>6184</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>20731</t>
+          <t>20482</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -7741,12 +7741,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>6,91%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -7761,12 +7761,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>5431</t>
+          <t>5486</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>22292</t>
+          <t>21799</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -7776,12 +7776,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,0%</t>
         </is>
       </c>
     </row>
@@ -7808,12 +7808,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>637078</t>
+          <t>637702</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>692109</t>
+          <t>690614</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -7823,12 +7823,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>73,13%</t>
+          <t>73,21%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>79,45%</t>
+          <t>79,28%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -7843,12 +7843,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>239895</t>
+          <t>241307</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>295315</t>
+          <t>294932</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -7858,12 +7858,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>32,15%</t>
+          <t>32,34%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>39,58%</t>
+          <t>39,53%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -7878,12 +7878,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>887821</t>
+          <t>888787</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>971263</t>
+          <t>971285</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -7893,7 +7893,7 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>54,9%</t>
+          <t>54,96%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
@@ -7926,7 +7926,7 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>11249</t>
+          <t>11048</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -7941,7 +7941,7 @@
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -7956,12 +7956,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>292984</t>
+          <t>297201</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>349248</t>
+          <t>351962</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -7971,12 +7971,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>39,27%</t>
+          <t>39,83%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>46,81%</t>
+          <t>47,17%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -7991,12 +7991,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>295256</t>
+          <t>293362</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>361475</t>
+          <t>360159</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -8006,12 +8006,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>18,26%</t>
+          <t>18,14%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>22,35%</t>
+          <t>22,27%</t>
         </is>
       </c>
     </row>
@@ -8034,12 +8034,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>119227</t>
+          <t>121248</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>166327</t>
+          <t>166025</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -8049,82 +8049,82 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
+          <t>13,92%</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>19,06%</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="K34" s="2" t="inlineStr">
+        <is>
+          <t>78409</t>
+        </is>
+      </c>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>62373</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>98199</t>
+        </is>
+      </c>
+      <c r="N34" s="2" t="inlineStr">
+        <is>
+          <t>10,51%</t>
+        </is>
+      </c>
+      <c r="O34" s="2" t="inlineStr">
+        <is>
+          <t>8,36%</t>
+        </is>
+      </c>
+      <c r="P34" s="2" t="inlineStr">
+        <is>
+          <t>13,16%</t>
+        </is>
+      </c>
+      <c r="Q34" s="2" t="inlineStr">
+        <is>
+          <t>198</t>
+        </is>
+      </c>
+      <c r="R34" s="2" t="inlineStr">
+        <is>
+          <t>221358</t>
+        </is>
+      </c>
+      <c r="S34" s="2" t="inlineStr">
+        <is>
+          <t>193943</t>
+        </is>
+      </c>
+      <c r="T34" s="2" t="inlineStr">
+        <is>
+          <t>253555</t>
+        </is>
+      </c>
+      <c r="U34" s="2" t="inlineStr">
+        <is>
           <t>13,69%</t>
         </is>
       </c>
-      <c r="I34" s="2" t="inlineStr">
-        <is>
-          <t>19,09%</t>
-        </is>
-      </c>
-      <c r="J34" s="2" t="inlineStr">
-        <is>
-          <t>69</t>
-        </is>
-      </c>
-      <c r="K34" s="2" t="inlineStr">
-        <is>
-          <t>78409</t>
-        </is>
-      </c>
-      <c r="L34" s="2" t="inlineStr">
-        <is>
-          <t>61610</t>
-        </is>
-      </c>
-      <c r="M34" s="2" t="inlineStr">
-        <is>
-          <t>97220</t>
-        </is>
-      </c>
-      <c r="N34" s="2" t="inlineStr">
-        <is>
-          <t>10,51%</t>
-        </is>
-      </c>
-      <c r="O34" s="2" t="inlineStr">
-        <is>
-          <t>8,26%</t>
-        </is>
-      </c>
-      <c r="P34" s="2" t="inlineStr">
-        <is>
-          <t>13,03%</t>
-        </is>
-      </c>
-      <c r="Q34" s="2" t="inlineStr">
-        <is>
-          <t>198</t>
-        </is>
-      </c>
-      <c r="R34" s="2" t="inlineStr">
-        <is>
-          <t>221358</t>
-        </is>
-      </c>
-      <c r="S34" s="2" t="inlineStr">
-        <is>
-          <t>194534</t>
-        </is>
-      </c>
-      <c r="T34" s="2" t="inlineStr">
-        <is>
-          <t>252031</t>
-        </is>
-      </c>
-      <c r="U34" s="2" t="inlineStr">
-        <is>
-          <t>13,69%</t>
-        </is>
-      </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>12,03%</t>
+          <t>11,99%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>15,58%</t>
+          <t>15,68%</t>
         </is>
       </c>
     </row>
@@ -8147,12 +8147,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>45583</t>
+          <t>44464</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>76997</t>
+          <t>77035</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -8162,7 +8162,7 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
@@ -8182,12 +8182,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>77718</t>
+          <t>78999</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>118426</t>
+          <t>119181</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -8197,12 +8197,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>10,42%</t>
+          <t>10,59%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>15,87%</t>
+          <t>15,97%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -8217,12 +8217,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>131474</t>
+          <t>131836</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>183044</t>
+          <t>181554</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -8232,12 +8232,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>8,15%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>11,32%</t>
+          <t>11,23%</t>
         </is>
       </c>
     </row>
@@ -8960,7 +8960,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>5989</t>
+          <t>5348</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8975,7 +8975,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>41,48%</t>
+          <t>37,04%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9030,7 +9030,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>6997</t>
+          <t>6226</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -9045,7 +9045,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>25,64%</t>
+          <t>22,82%</t>
         </is>
       </c>
     </row>
@@ -9181,12 +9181,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1934</t>
+          <t>1931</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>9301</t>
+          <t>8969</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -9196,12 +9196,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>13,39%</t>
+          <t>13,37%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>64,41%</t>
+          <t>62,11%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9221,7 +9221,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5868</t>
+          <t>5392</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -9236,7 +9236,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>45,67%</t>
+          <t>41,96%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9251,12 +9251,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2961</t>
+          <t>2930</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>11832</t>
+          <t>11770</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9266,12 +9266,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>10,85%</t>
+          <t>10,74%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>43,36%</t>
+          <t>43,13%</t>
         </is>
       </c>
     </row>
@@ -9294,12 +9294,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3218</t>
+          <t>4093</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>11366</t>
+          <t>11518</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -9309,12 +9309,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>22,29%</t>
+          <t>28,34%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>78,71%</t>
+          <t>79,76%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9329,7 +9329,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>6982</t>
+          <t>7458</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -9344,7 +9344,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>54,33%</t>
+          <t>58,04%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -9364,12 +9364,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>13306</t>
+          <t>13215</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>22546</t>
+          <t>23239</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -9379,12 +9379,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>48,76%</t>
+          <t>48,43%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>82,62%</t>
+          <t>85,16%</t>
         </is>
       </c>
     </row>
@@ -9416,7 +9416,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>3808</t>
+          <t>5617</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -9431,7 +9431,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>12,9%</t>
+          <t>19,02%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -9446,12 +9446,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>811</t>
+          <t>821</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>7145</t>
+          <t>6268</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -9461,12 +9461,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>24,94%</t>
+          <t>21,88%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -9481,12 +9481,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>887</t>
+          <t>878</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>8341</t>
+          <t>7938</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9496,12 +9496,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>14,34%</t>
+          <t>13,65%</t>
         </is>
       </c>
     </row>
@@ -9529,7 +9529,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4438</t>
+          <t>4716</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9544,7 +9544,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>15,03%</t>
+          <t>15,97%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9559,12 +9559,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>925</t>
+          <t>929</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>8412</t>
+          <t>8329</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9574,12 +9574,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>29,37%</t>
+          <t>29,07%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9594,12 +9594,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1766</t>
+          <t>1831</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>10276</t>
+          <t>10044</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9609,12 +9609,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>17,66%</t>
+          <t>17,27%</t>
         </is>
       </c>
     </row>
@@ -9637,12 +9637,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>9791</t>
+          <t>10151</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>21014</t>
+          <t>20862</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9652,12 +9652,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>33,16%</t>
+          <t>34,38%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>71,17%</t>
+          <t>70,66%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9672,12 +9672,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3373</t>
+          <t>2961</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>12638</t>
+          <t>12905</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9687,12 +9687,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>11,77%</t>
+          <t>10,34%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>44,12%</t>
+          <t>45,05%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9707,12 +9707,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>15856</t>
+          <t>15336</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>30350</t>
+          <t>30835</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9722,12 +9722,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>27,26%</t>
+          <t>26,36%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>52,17%</t>
+          <t>53,01%</t>
         </is>
       </c>
     </row>
@@ -9750,12 +9750,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>7223</t>
+          <t>6513</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>17853</t>
+          <t>17754</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -9765,12 +9765,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>24,46%</t>
+          <t>22,06%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>60,47%</t>
+          <t>60,13%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -9785,12 +9785,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>11184</t>
+          <t>10204</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>21222</t>
+          <t>21245</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -9800,12 +9800,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>39,04%</t>
+          <t>35,62%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>74,08%</t>
+          <t>74,16%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -9820,12 +9820,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>21012</t>
+          <t>20547</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>35994</t>
+          <t>36021</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -9835,12 +9835,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>36,12%</t>
+          <t>35,32%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>61,88%</t>
+          <t>61,92%</t>
         </is>
       </c>
     </row>
@@ -9867,12 +9867,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>18794</t>
+          <t>17987</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>36195</t>
+          <t>36050</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -9882,12 +9882,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>23,84%</t>
+          <t>22,82%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>45,92%</t>
+          <t>45,74%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9902,12 +9902,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>6209</t>
+          <t>5982</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>17933</t>
+          <t>17602</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9917,12 +9917,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>13,12%</t>
+          <t>12,64%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>37,88%</t>
+          <t>37,18%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9937,12 +9937,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>28494</t>
+          <t>26590</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>49314</t>
+          <t>49514</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9952,12 +9952,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>22,59%</t>
+          <t>21,08%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>39,09%</t>
+          <t>39,25%</t>
         </is>
       </c>
     </row>
@@ -10015,12 +10015,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>5790</t>
+          <t>6138</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>18032</t>
+          <t>17788</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -10030,12 +10030,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>12,23%</t>
+          <t>12,97%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>38,09%</t>
+          <t>37,58%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10050,12 +10050,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6325</t>
+          <t>6179</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>19911</t>
+          <t>19425</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10065,12 +10065,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>15,78%</t>
+          <t>15,4%</t>
         </is>
       </c>
     </row>
@@ -10093,12 +10093,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>24898</t>
+          <t>25921</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>42835</t>
+          <t>43293</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -10108,12 +10108,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>31,59%</t>
+          <t>32,89%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>54,35%</t>
+          <t>54,93%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -10128,12 +10128,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>9639</t>
+          <t>9325</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>23366</t>
+          <t>22830</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -10143,12 +10143,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>20,36%</t>
+          <t>19,7%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>49,36%</t>
+          <t>48,23%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -10163,12 +10163,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>38927</t>
+          <t>38494</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>61389</t>
+          <t>61771</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -10178,12 +10178,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>30,86%</t>
+          <t>30,51%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>48,66%</t>
+          <t>48,96%</t>
         </is>
       </c>
     </row>
@@ -10206,12 +10206,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>11471</t>
+          <t>11670</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>26463</t>
+          <t>27991</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -10221,12 +10221,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>14,55%</t>
+          <t>14,81%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>33,57%</t>
+          <t>35,51%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -10241,12 +10241,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>4300</t>
+          <t>4163</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>14888</t>
+          <t>15453</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -10256,12 +10256,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>9,08%</t>
+          <t>8,79%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>31,45%</t>
+          <t>32,64%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10276,12 +10276,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>18191</t>
+          <t>18206</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>38261</t>
+          <t>37584</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -10291,12 +10291,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>14,42%</t>
+          <t>14,43%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>30,33%</t>
+          <t>29,79%</t>
         </is>
       </c>
     </row>
@@ -10323,12 +10323,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>140822</t>
+          <t>141658</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>165245</t>
+          <t>165247</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -10338,7 +10338,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>70,3%</t>
+          <t>70,72%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -10358,12 +10358,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>36972</t>
+          <t>36785</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>58232</t>
+          <t>57912</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -10373,12 +10373,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>33,31%</t>
+          <t>33,14%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>52,46%</t>
+          <t>52,18%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10393,12 +10393,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>183891</t>
+          <t>183914</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>218805</t>
+          <t>220302</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -10408,12 +10408,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>59,07%</t>
+          <t>59,08%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>70,29%</t>
+          <t>70,77%</t>
         </is>
       </c>
     </row>
@@ -10471,12 +10471,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>24070</t>
+          <t>24364</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>44220</t>
+          <t>44150</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -10486,12 +10486,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>21,69%</t>
+          <t>21,95%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>39,84%</t>
+          <t>39,78%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -10506,12 +10506,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>23166</t>
+          <t>23266</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>47062</t>
+          <t>45470</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -10521,12 +10521,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>7,47%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>15,12%</t>
+          <t>14,61%</t>
         </is>
       </c>
     </row>
@@ -10549,12 +10549,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>21558</t>
+          <t>21280</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>43993</t>
+          <t>42417</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10564,12 +10564,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>10,76%</t>
+          <t>10,62%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>21,96%</t>
+          <t>21,18%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10584,12 +10584,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>13118</t>
+          <t>13306</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>30102</t>
+          <t>29598</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10599,12 +10599,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>11,82%</t>
+          <t>11,99%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>27,12%</t>
+          <t>26,67%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10619,12 +10619,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>39934</t>
+          <t>37780</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>68231</t>
+          <t>66153</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10634,12 +10634,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>12,83%</t>
+          <t>12,14%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>21,92%</t>
+          <t>21,25%</t>
         </is>
       </c>
     </row>
@@ -10662,12 +10662,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>8745</t>
+          <t>8685</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>25397</t>
+          <t>23951</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10677,12 +10677,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>12,68%</t>
+          <t>11,96%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10697,12 +10697,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>5163</t>
+          <t>5166</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>19993</t>
+          <t>18558</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10717,7 +10717,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>18,01%</t>
+          <t>16,72%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10732,12 +10732,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>17155</t>
+          <t>17054</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>37024</t>
+          <t>37614</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10747,12 +10747,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>11,89%</t>
+          <t>12,08%</t>
         </is>
       </c>
     </row>
@@ -10779,7 +10779,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>315948</t>
+          <t>315991</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -10794,7 +10794,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>97,74%</t>
+          <t>97,75%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -10814,12 +10814,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>126466</t>
+          <t>125210</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>157144</t>
+          <t>156934</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10829,12 +10829,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>54,03%</t>
+          <t>53,5%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>67,14%</t>
+          <t>67,05%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -10849,12 +10849,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>443640</t>
+          <t>444304</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>481414</t>
+          <t>481959</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -10864,12 +10864,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>79,6%</t>
+          <t>79,72%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>86,38%</t>
+          <t>86,48%</t>
         </is>
       </c>
     </row>
@@ -10927,12 +10927,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>54091</t>
+          <t>54026</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>83595</t>
+          <t>81727</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -10942,12 +10942,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>23,11%</t>
+          <t>23,08%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>35,72%</t>
+          <t>34,92%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10962,12 +10962,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>53146</t>
+          <t>51799</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>84073</t>
+          <t>83368</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10977,12 +10977,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>9,54%</t>
+          <t>9,29%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>15,09%</t>
+          <t>14,96%</t>
         </is>
       </c>
     </row>
@@ -11010,7 +11010,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>5498</t>
+          <t>5330</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -11025,7 +11025,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -11040,12 +11040,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1012</t>
+          <t>1079</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>9428</t>
+          <t>9723</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -11055,12 +11055,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -11075,12 +11075,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1906</t>
+          <t>1989</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>11412</t>
+          <t>11534</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -11090,12 +11090,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,07%</t>
         </is>
       </c>
     </row>
@@ -11123,7 +11123,7 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>5229</t>
+          <t>6157</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -11138,7 +11138,7 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -11153,12 +11153,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>15012</t>
+          <t>14919</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>34371</t>
+          <t>32963</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -11168,12 +11168,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>14,69%</t>
+          <t>14,08%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -11188,12 +11188,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>14613</t>
+          <t>15099</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>34573</t>
+          <t>35234</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -11203,12 +11203,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>6,32%</t>
         </is>
       </c>
     </row>
@@ -11235,7 +11235,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>242351</t>
+          <t>243243</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -11250,7 +11250,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>96,79%</t>
+          <t>97,14%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -11270,12 +11270,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>96000</t>
+          <t>95261</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>132911</t>
+          <t>131698</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -11285,12 +11285,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>32,82%</t>
+          <t>32,56%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>45,43%</t>
+          <t>45,02%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -11305,12 +11305,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>339461</t>
+          <t>337018</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>388587</t>
+          <t>385979</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -11320,12 +11320,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>62,52%</t>
+          <t>62,07%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>71,57%</t>
+          <t>71,09%</t>
         </is>
       </c>
     </row>
@@ -11383,12 +11383,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>129076</t>
+          <t>129110</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>168174</t>
+          <t>168770</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -11398,12 +11398,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>44,12%</t>
+          <t>44,13%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>57,49%</t>
+          <t>57,69%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -11418,12 +11418,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>123916</t>
+          <t>124663</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>172789</t>
+          <t>170445</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -11433,12 +11433,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>22,82%</t>
+          <t>22,96%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>31,82%</t>
+          <t>31,39%</t>
         </is>
       </c>
     </row>
@@ -11466,7 +11466,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>6360</t>
+          <t>6331</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -11481,7 +11481,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -11496,12 +11496,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>1231</t>
+          <t>1237</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>11759</t>
+          <t>10608</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -11516,7 +11516,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -11531,12 +11531,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>2219</t>
+          <t>1793</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>12551</t>
+          <t>13275</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -11546,12 +11546,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,45%</t>
         </is>
       </c>
     </row>
@@ -11579,7 +11579,7 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>5017</t>
+          <t>3645</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -11594,7 +11594,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -11609,12 +11609,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>17830</t>
+          <t>17847</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>42691</t>
+          <t>42307</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -11624,12 +11624,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>14,59%</t>
+          <t>14,46%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -11644,12 +11644,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>18438</t>
+          <t>19219</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>43106</t>
+          <t>43401</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -11659,12 +11659,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>7,99%</t>
         </is>
       </c>
     </row>
@@ -11691,12 +11691,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>726361</t>
+          <t>730260</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>774060</t>
+          <t>775679</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -11706,12 +11706,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>80,6%</t>
+          <t>81,03%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>85,89%</t>
+          <t>86,07%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -11726,12 +11726,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>288316</t>
+          <t>288692</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>346981</t>
+          <t>346949</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -11741,12 +11741,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>39,12%</t>
+          <t>39,17%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>47,08%</t>
+          <t>47,07%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -11761,12 +11761,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>1028731</t>
+          <t>1033720</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>1105522</t>
+          <t>1108884</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -11776,12 +11776,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>62,79%</t>
+          <t>63,1%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>67,48%</t>
+          <t>67,69%</t>
         </is>
       </c>
     </row>
@@ -11809,7 +11809,7 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>5233</t>
+          <t>5593</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -11824,7 +11824,7 @@
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -11839,12 +11839,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>235152</t>
+          <t>236685</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>292433</t>
+          <t>291509</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -11854,12 +11854,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>31,9%</t>
+          <t>32,11%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>39,68%</t>
+          <t>39,55%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -11874,12 +11874,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>236126</t>
+          <t>234246</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>298549</t>
+          <t>297540</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -11889,12 +11889,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>14,41%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>18,22%</t>
+          <t>18,16%</t>
         </is>
       </c>
     </row>
@@ -11917,12 +11917,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>71692</t>
+          <t>71919</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>106875</t>
+          <t>107131</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -11932,12 +11932,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>7,95%</t>
+          <t>7,98%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>11,86%</t>
+          <t>11,89%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -11952,12 +11952,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>40367</t>
+          <t>40608</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>72055</t>
+          <t>70976</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -11967,12 +11967,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>5,51%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>9,78%</t>
+          <t>9,63%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -11987,12 +11987,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>119274</t>
+          <t>118089</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>166609</t>
+          <t>164143</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -12002,12 +12002,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>7,21%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>10,17%</t>
+          <t>10,02%</t>
         </is>
       </c>
     </row>
@@ -12030,12 +12030,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>44849</t>
+          <t>45244</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>75868</t>
+          <t>76195</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -12045,12 +12045,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>8,42%</t>
+          <t>8,45%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -12065,12 +12065,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>90297</t>
+          <t>88792</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>132020</t>
+          <t>129165</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -12080,12 +12080,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>12,25%</t>
+          <t>12,05%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>17,91%</t>
+          <t>17,52%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -12100,12 +12100,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>145433</t>
+          <t>144074</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>195121</t>
+          <t>193592</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -12115,12 +12115,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>8,88%</t>
+          <t>8,79%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>11,91%</t>
+          <t>11,82%</t>
         </is>
       </c>
     </row>
@@ -12638,7 +12638,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>3268</t>
+          <t>3160</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
@@ -12673,7 +12673,7 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>3268</t>
+          <t>3161</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
@@ -12683,12 +12683,12 @@
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>5258</t>
+          <t>4914</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>62,16%</t>
+          <t>64,32%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
@@ -12716,7 +12716,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1990</t>
+          <t>1753</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -12786,7 +12786,7 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>1990</t>
+          <t>1753</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
@@ -12796,12 +12796,12 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>5258</t>
+          <t>4914</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>37,84%</t>
+          <t>35,68%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
@@ -12946,7 +12946,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2381</t>
+          <t>2458</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -12956,12 +12956,12 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6818</t>
+          <t>6573</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>29,31%</t>
+          <t>29,4%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -12971,7 +12971,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>83,93%</t>
+          <t>78,6%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -12981,7 +12981,7 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1181</t>
+          <t>1115</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
@@ -12991,12 +12991,12 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>5260</t>
+          <t>5195</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>8,48%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
@@ -13006,7 +13006,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>43,64%</t>
+          <t>39,52%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -13016,32 +13016,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>3562</t>
+          <t>3573</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1076</t>
+          <t>1046</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>9072</t>
+          <t>9132</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>17,65%</t>
+          <t>16,61%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>44,96%</t>
+          <t>42,46%</t>
         </is>
       </c>
     </row>
@@ -13059,7 +13059,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>1140</t>
+          <t>1294</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -13069,12 +13069,12 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4807</t>
+          <t>5592</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>14,03%</t>
+          <t>15,47%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -13084,7 +13084,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>59,18%</t>
+          <t>66,87%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -13094,7 +13094,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>1535</t>
+          <t>1463</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
@@ -13104,12 +13104,12 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>6314</t>
+          <t>6545</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>12,73%</t>
+          <t>11,13%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
@@ -13119,7 +13119,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>52,37%</t>
+          <t>49,79%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -13129,7 +13129,7 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>2675</t>
+          <t>2757</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
@@ -13139,12 +13139,12 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>8583</t>
+          <t>8477</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>13,25%</t>
+          <t>12,82%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
@@ -13154,7 +13154,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>42,53%</t>
+          <t>39,41%</t>
         </is>
       </c>
     </row>
@@ -13172,32 +13172,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4602</t>
+          <t>4610</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1349</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>7166</t>
+          <t>7358</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>56,66%</t>
+          <t>55,13%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>16,13%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>88,22%</t>
+          <t>88,0%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -13207,27 +13207,27 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>9339</t>
+          <t>10568</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>4787</t>
+          <t>6379</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>12055</t>
+          <t>13146</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>77,47%</t>
+          <t>80,39%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>39,71%</t>
+          <t>48,52%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -13242,32 +13242,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>13941</t>
+          <t>15178</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>9057</t>
+          <t>9911</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>17746</t>
+          <t>19265</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>69,09%</t>
+          <t>70,57%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>44,89%</t>
+          <t>46,08%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>87,95%</t>
+          <t>89,57%</t>
         </is>
       </c>
     </row>
@@ -13324,7 +13324,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>734</t>
+          <t>746</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
@@ -13334,12 +13334,12 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>3784</t>
+          <t>3736</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
@@ -13349,7 +13349,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>14,64%</t>
+          <t>13,38%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -13359,7 +13359,7 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>734</t>
+          <t>746</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
@@ -13369,12 +13369,12 @@
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>3906</t>
+          <t>3951</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
@@ -13384,7 +13384,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>8,54%</t>
+          <t>8,1%</t>
         </is>
       </c>
     </row>
@@ -13402,32 +13402,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>7266</t>
+          <t>7674</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3213</t>
+          <t>3257</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>11826</t>
+          <t>12746</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>36,57%</t>
+          <t>36,83%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>16,17%</t>
+          <t>15,63%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>59,51%</t>
+          <t>61,18%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -13437,32 +13437,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>5349</t>
+          <t>5705</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2444</t>
+          <t>2640</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>9023</t>
+          <t>9837</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>20,69%</t>
+          <t>20,42%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>9,46%</t>
+          <t>9,45%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>34,9%</t>
+          <t>35,22%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -13472,32 +13472,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>12615</t>
+          <t>13379</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>7686</t>
+          <t>8001</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>18860</t>
+          <t>19804</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>27,59%</t>
+          <t>27,43%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>16,81%</t>
+          <t>16,41%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>41,25%</t>
+          <t>40,61%</t>
         </is>
       </c>
     </row>
@@ -13515,7 +13515,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>2080</t>
+          <t>2312</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -13525,12 +13525,12 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>6265</t>
+          <t>6729</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>10,47%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -13540,7 +13540,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>31,53%</t>
+          <t>32,3%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -13550,32 +13550,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>3475</t>
+          <t>4101</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1242</t>
+          <t>1465</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>7350</t>
+          <t>7801</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>13,44%</t>
+          <t>14,68%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>28,43%</t>
+          <t>27,93%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -13585,32 +13585,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>5556</t>
+          <t>6412</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>2449</t>
+          <t>2784</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>10713</t>
+          <t>12152</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>12,15%</t>
+          <t>13,15%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>23,43%</t>
+          <t>24,92%</t>
         </is>
       </c>
     </row>
@@ -13628,32 +13628,32 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>10525</t>
+          <t>10849</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>6042</t>
+          <t>6079</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>14987</t>
+          <t>15505</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>52,96%</t>
+          <t>52,07%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>30,41%</t>
+          <t>29,18%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>75,42%</t>
+          <t>74,42%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -13663,32 +13663,32 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>16295</t>
+          <t>17380</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>11799</t>
+          <t>13165</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>19704</t>
+          <t>21533</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>63,03%</t>
+          <t>62,22%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>45,64%</t>
+          <t>47,13%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>76,22%</t>
+          <t>77,09%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -13698,32 +13698,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>26820</t>
+          <t>28230</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>20528</t>
+          <t>21736</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>32738</t>
+          <t>34394</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>58,65%</t>
+          <t>57,89%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>44,89%</t>
+          <t>44,57%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>71,6%</t>
+          <t>70,53%</t>
         </is>
       </c>
     </row>
@@ -13745,32 +13745,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>8507</t>
+          <t>8811</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3689</t>
+          <t>3895</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>15147</t>
+          <t>16734</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>15,58%</t>
+          <t>14,51%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>27,74%</t>
+          <t>27,56%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -13780,32 +13780,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>2608</t>
+          <t>2646</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>770</t>
+          <t>743</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>6589</t>
+          <t>6608</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>16,49%</t>
+          <t>14,78%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -13815,32 +13815,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>11115</t>
+          <t>11457</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>5799</t>
+          <t>5408</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>18427</t>
+          <t>18884</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>11,76%</t>
+          <t>10,87%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>5,13%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>19,49%</t>
+          <t>17,91%</t>
         </is>
       </c>
     </row>
@@ -13858,32 +13858,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>28304</t>
+          <t>30287</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>20824</t>
+          <t>21743</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>35941</t>
+          <t>38891</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>51,84%</t>
+          <t>49,88%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>38,14%</t>
+          <t>35,81%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>65,83%</t>
+          <t>64,05%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -13893,32 +13893,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>11583</t>
+          <t>12228</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>7583</t>
+          <t>7933</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>15976</t>
+          <t>17061</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>29,0%</t>
+          <t>27,34%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>18,98%</t>
+          <t>17,74%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>39,99%</t>
+          <t>38,15%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -13928,32 +13928,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>39887</t>
+          <t>42515</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>31525</t>
+          <t>33659</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>48771</t>
+          <t>52040</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>42,19%</t>
+          <t>40,32%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>33,34%</t>
+          <t>31,92%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>51,59%</t>
+          <t>49,36%</t>
         </is>
       </c>
     </row>
@@ -14006,32 +14006,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>9295</t>
+          <t>10072</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>5732</t>
+          <t>5858</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>14119</t>
+          <t>14812</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>23,27%</t>
+          <t>22,52%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>14,35%</t>
+          <t>13,1%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>35,34%</t>
+          <t>33,12%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -14041,32 +14041,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>9295</t>
+          <t>10072</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>5112</t>
+          <t>6078</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>14631</t>
+          <t>16051</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>9,83%</t>
+          <t>9,55%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,76%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>15,48%</t>
+          <t>15,22%</t>
         </is>
       </c>
     </row>
@@ -14084,32 +14084,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>17786</t>
+          <t>21618</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>11406</t>
+          <t>14054</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>24976</t>
+          <t>29507</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>32,58%</t>
+          <t>35,6%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>20,89%</t>
+          <t>23,15%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>45,75%</t>
+          <t>48,6%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -14119,32 +14119,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>16461</t>
+          <t>19776</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>12005</t>
+          <t>14607</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>21578</t>
+          <t>25121</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>41,21%</t>
+          <t>44,22%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>30,05%</t>
+          <t>32,66%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>54,02%</t>
+          <t>56,17%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -14154,32 +14154,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>34246</t>
+          <t>41394</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>26441</t>
+          <t>32659</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>43071</t>
+          <t>50892</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>36,22%</t>
+          <t>39,26%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>27,97%</t>
+          <t>30,97%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>45,56%</t>
+          <t>48,27%</t>
         </is>
       </c>
     </row>
@@ -14201,32 +14201,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>61812</t>
+          <t>64865</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>49022</t>
+          <t>52498</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>73621</t>
+          <t>75051</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>36,32%</t>
+          <t>36,13%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>28,8%</t>
+          <t>29,24%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>43,25%</t>
+          <t>41,8%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -14236,32 +14236,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>20246</t>
+          <t>22656</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>15240</t>
+          <t>16812</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>26699</t>
+          <t>30325</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>19,06%</t>
+          <t>19,3%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>14,35%</t>
+          <t>14,32%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>25,14%</t>
+          <t>25,83%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -14271,32 +14271,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>82058</t>
+          <t>87521</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>69822</t>
+          <t>73762</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>97180</t>
+          <t>103460</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>29,69%</t>
+          <t>29,48%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>25,26%</t>
+          <t>24,84%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>35,16%</t>
+          <t>34,84%</t>
         </is>
       </c>
     </row>
@@ -14314,32 +14314,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>51636</t>
+          <t>52988</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>40886</t>
+          <t>42886</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>63542</t>
+          <t>67064</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>30,34%</t>
+          <t>29,51%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>24,02%</t>
+          <t>23,89%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>37,33%</t>
+          <t>37,36%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -14349,32 +14349,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>20151</t>
+          <t>22610</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>14295</t>
+          <t>16381</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>26147</t>
+          <t>30382</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>18,98%</t>
+          <t>19,26%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>13,46%</t>
+          <t>13,95%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>24,62%</t>
+          <t>25,88%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -14384,32 +14384,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>71787</t>
+          <t>75597</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>59582</t>
+          <t>62927</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>86390</t>
+          <t>90126</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>25,97%</t>
+          <t>25,46%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>21,56%</t>
+          <t>21,19%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>31,26%</t>
+          <t>30,35%</t>
         </is>
       </c>
     </row>
@@ -14427,32 +14427,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>5356</t>
+          <t>5426</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1982</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>11372</t>
+          <t>11302</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -14462,32 +14462,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>35002</t>
+          <t>37412</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>27625</t>
+          <t>30404</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>42073</t>
+          <t>46141</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>32,96%</t>
+          <t>31,87%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>26,01%</t>
+          <t>25,9%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>39,62%</t>
+          <t>39,31%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -14497,32 +14497,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>40358</t>
+          <t>42838</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>32151</t>
+          <t>33106</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>49828</t>
+          <t>53605</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>14,6%</t>
+          <t>14,43%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>11,63%</t>
+          <t>11,15%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>18,03%</t>
+          <t>18,05%</t>
         </is>
       </c>
     </row>
@@ -14540,32 +14540,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>51405</t>
+          <t>56250</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>40998</t>
+          <t>45336</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>63699</t>
+          <t>68720</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>30,2%</t>
+          <t>31,33%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>24,09%</t>
+          <t>25,25%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>37,42%</t>
+          <t>38,28%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -14575,32 +14575,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>30797</t>
+          <t>34714</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>23614</t>
+          <t>27769</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>38298</t>
+          <t>43095</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>29,0%</t>
+          <t>29,57%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>22,24%</t>
+          <t>23,65%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>36,06%</t>
+          <t>36,71%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -14610,32 +14610,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>82202</t>
+          <t>90964</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>69385</t>
+          <t>76531</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>95588</t>
+          <t>105067</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>29,74%</t>
+          <t>30,64%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>25,1%</t>
+          <t>25,78%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>34,58%</t>
+          <t>35,39%</t>
         </is>
       </c>
     </row>
@@ -14657,32 +14657,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>185644</t>
+          <t>205425</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>172178</t>
+          <t>189228</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>198080</t>
+          <t>219238</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>61,98%</t>
+          <t>61,95%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>57,49%</t>
+          <t>57,07%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>66,13%</t>
+          <t>66,12%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -14692,32 +14692,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>324154</t>
+          <t>133108</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>221401</t>
+          <t>122490</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>399353</t>
+          <t>145072</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>75,16%</t>
+          <t>53,48%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>51,34%</t>
+          <t>49,22%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>92,6%</t>
+          <t>58,29%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -14727,32 +14727,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>509798</t>
+          <t>338533</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>416629</t>
+          <t>319279</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>633700</t>
+          <t>356097</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>69,76%</t>
+          <t>58,32%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>57,01%</t>
+          <t>55,0%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>86,72%</t>
+          <t>61,35%</t>
         </is>
       </c>
     </row>
@@ -14770,32 +14770,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>24616</t>
+          <t>25551</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>18181</t>
+          <t>18975</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>32915</t>
+          <t>34503</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>7,71%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>5,72%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>10,99%</t>
+          <t>10,41%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -14805,32 +14805,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>10079</t>
+          <t>10767</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>2637</t>
+          <t>6801</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>21674</t>
+          <t>16971</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>6,82%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -14840,32 +14840,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>34695</t>
+          <t>36319</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>16073</t>
+          <t>27900</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>52525</t>
+          <t>46994</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>8,1%</t>
         </is>
       </c>
     </row>
@@ -14883,32 +14883,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>2571</t>
+          <t>2610</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>886</t>
+          <t>940</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>5803</t>
+          <t>6473</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -14918,32 +14918,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>49291</t>
+          <t>52452</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>12952</t>
+          <t>43736</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>99230</t>
+          <t>62705</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>11,43%</t>
+          <t>21,08%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>17,57%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>23,01%</t>
+          <t>25,2%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -14953,32 +14953,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>51862</t>
+          <t>55062</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>24179</t>
+          <t>46698</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>77153</t>
+          <t>66144</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>9,49%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>8,05%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>10,56%</t>
+          <t>11,4%</t>
         </is>
       </c>
     </row>
@@ -14996,32 +14996,32 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>86686</t>
+          <t>97995</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>74525</t>
+          <t>84254</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>98235</t>
+          <t>111133</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>28,94%</t>
+          <t>29,55%</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>24,88%</t>
+          <t>25,41%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>32,8%</t>
+          <t>33,52%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -15031,32 +15031,32 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>47741</t>
+          <t>52548</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>14875</t>
+          <t>44387</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>96165</t>
+          <t>62018</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>11,07%</t>
+          <t>21,11%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>17,83%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>22,3%</t>
+          <t>24,92%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -15066,32 +15066,32 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>134426</t>
+          <t>150543</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>57518</t>
+          <t>133641</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>193163</t>
+          <t>167626</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>18,39%</t>
+          <t>25,94%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>7,87%</t>
+          <t>23,02%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>26,43%</t>
+          <t>28,88%</t>
         </is>
       </c>
     </row>
@@ -15113,32 +15113,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>162416</t>
+          <t>178598</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>150315</t>
+          <t>166109</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>173371</t>
+          <t>190785</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>65,71%</t>
+          <t>65,74%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>60,82%</t>
+          <t>61,14%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>70,14%</t>
+          <t>70,23%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -15148,32 +15148,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>88341</t>
+          <t>98463</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>77170</t>
+          <t>85953</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>99799</t>
+          <t>110952</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>27,69%</t>
+          <t>28,24%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>24,19%</t>
+          <t>24,66%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>31,28%</t>
+          <t>31,83%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -15183,32 +15183,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>250757</t>
+          <t>277061</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>234072</t>
+          <t>257370</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>269132</t>
+          <t>296780</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>44,29%</t>
+          <t>44,67%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>41,34%</t>
+          <t>41,49%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>47,53%</t>
+          <t>47,84%</t>
         </is>
       </c>
     </row>
@@ -15226,32 +15226,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>15402</t>
+          <t>16417</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>10708</t>
+          <t>11133</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>22216</t>
+          <t>23439</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>6,04%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>8,99%</t>
+          <t>8,63%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -15261,32 +15261,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>12633</t>
+          <t>13740</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>8846</t>
+          <t>8755</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>18361</t>
+          <t>18756</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -15296,22 +15296,22 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>28035</t>
+          <t>30157</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>21209</t>
+          <t>23285</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>36226</t>
+          <t>39562</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
@@ -15321,7 +15321,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>6,38%</t>
         </is>
       </c>
     </row>
@@ -15374,32 +15374,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>186482</t>
+          <t>202546</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>174562</t>
+          <t>188928</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>199108</t>
+          <t>217357</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>58,46%</t>
+          <t>58,1%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>54,72%</t>
+          <t>54,19%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>62,41%</t>
+          <t>62,35%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -15409,32 +15409,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>186482</t>
+          <t>202546</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>170683</t>
+          <t>184877</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>201449</t>
+          <t>221463</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>32,94%</t>
+          <t>32,65%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>30,15%</t>
+          <t>29,8%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>35,58%</t>
+          <t>35,7%</t>
         </is>
       </c>
     </row>
@@ -15452,22 +15452,22 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>69347</t>
+          <t>76661</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>59180</t>
+          <t>65030</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>80220</t>
+          <t>89731</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>28,06%</t>
+          <t>28,22%</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
@@ -15477,7 +15477,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>32,46%</t>
+          <t>33,03%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -15487,32 +15487,32 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>31556</t>
+          <t>33872</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>24285</t>
+          <t>26278</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>38875</t>
+          <t>43730</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>9,89%</t>
+          <t>9,72%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>7,54%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>12,19%</t>
+          <t>12,54%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -15522,17 +15522,17 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>100902</t>
+          <t>110533</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>87002</t>
+          <t>94512</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>115680</t>
+          <t>127405</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -15542,12 +15542,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>15,37%</t>
+          <t>15,24%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>20,43%</t>
+          <t>20,54%</t>
         </is>
       </c>
     </row>
@@ -15569,32 +15569,32 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>418379</t>
+          <t>457699</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>395485</t>
+          <t>430253</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>444252</t>
+          <t>485431</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>52,2%</t>
+          <t>52,34%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>49,34%</t>
+          <t>49,2%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>55,43%</t>
+          <t>55,51%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -15604,32 +15604,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>436084</t>
+          <t>257619</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>286160</t>
+          <t>238666</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>674187</t>
+          <t>279168</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>46,51%</t>
+          <t>32,05%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>30,52%</t>
+          <t>29,69%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>71,91%</t>
+          <t>34,73%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -15639,32 +15639,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>854463</t>
+          <t>715317</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>725456</t>
+          <t>683385</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>1152980</t>
+          <t>748748</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>49,13%</t>
+          <t>42,62%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>41,72%</t>
+          <t>40,72%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>66,3%</t>
+          <t>44,61%</t>
         </is>
       </c>
     </row>
@@ -15682,32 +15682,32 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>129604</t>
+          <t>135375</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>111262</t>
+          <t>116805</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>149374</t>
+          <t>157654</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>16,17%</t>
+          <t>15,48%</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>13,88%</t>
+          <t>13,36%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>18,64%</t>
+          <t>18,03%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -15717,32 +15717,32 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>60976</t>
+          <t>66164</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>29778</t>
+          <t>55192</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>83927</t>
+          <t>78578</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>8,23%</t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>6,87%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>8,95%</t>
+          <t>9,78%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -15752,32 +15752,32 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>190581</t>
+          <t>201539</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>122995</t>
+          <t>181275</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>224531</t>
+          <t>227978</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
         <is>
-          <t>10,96%</t>
+          <t>12,01%</t>
         </is>
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>10,8%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>12,91%</t>
+          <t>13,58%</t>
         </is>
       </c>
     </row>
@@ -15795,32 +15795,32 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>11148</t>
+          <t>11641</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>6516</t>
+          <t>6342</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>18862</t>
+          <t>19634</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -15830,32 +15830,32 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>288348</t>
+          <t>311206</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>150140</t>
+          <t>291430</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>379394</t>
+          <t>332244</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>30,75%</t>
+          <t>38,71%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>16,01%</t>
+          <t>36,25%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>40,46%</t>
+          <t>41,33%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -15865,32 +15865,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>299495</t>
+          <t>322848</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>198670</t>
+          <t>299363</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>349740</t>
+          <t>350622</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>17,22%</t>
+          <t>19,24%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>11,42%</t>
+          <t>17,84%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>20,11%</t>
+          <t>20,89%</t>
         </is>
       </c>
     </row>
@@ -15908,32 +15908,32 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>242339</t>
+          <t>269735</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>217117</t>
+          <t>244560</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>264657</t>
+          <t>294498</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>30,24%</t>
+          <t>30,85%</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>27,09%</t>
+          <t>27,97%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>33,02%</t>
+          <t>33,68%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -15943,32 +15943,32 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>152188</t>
+          <t>168859</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>78212</t>
+          <t>150263</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>203284</t>
+          <t>186524</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>16,23%</t>
+          <t>21,01%</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>8,34%</t>
+          <t>18,69%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>21,68%</t>
+          <t>23,2%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -15978,32 +15978,32 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>394527</t>
+          <t>438594</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>255174</t>
+          <t>408488</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>457237</t>
+          <t>471254</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>22,69%</t>
+          <t>26,13%</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>14,67%</t>
+          <t>24,34%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>26,29%</t>
+          <t>28,08%</t>
         </is>
       </c>
     </row>
